--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1,114 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Good Side\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EC07FA-559A-4965-BDC6-E3AED63FEE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
+    <sheet name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>ফাইলের নাম</t>
-  </si>
-  <si>
-    <t>ধরন</t>
-  </si>
-  <si>
-    <t>Caption / Text</t>
-  </si>
-  <si>
-    <t>Schedule Time</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>পোস্ট ID</t>
-  </si>
-  <si>
-    <t>নোট</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>1.png</t>
-  </si>
-  <si>
-    <t>#bestrong #motivation #upliftinglife #lifelessons</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF856404"/>
       <sz val="10"/>
-      <color rgb="FF856404"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -157,37 +92,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -507,413 +501,441 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CAA70D-E652-488D-91B8-DAA4C7450532}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="74.42578125" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="42.85546875" customWidth="1"/>
-    <col min="8" max="8" width="37.85546875" customWidth="1"/>
+    <col width="9.140625" customWidth="1" style="3" min="1" max="1"/>
+    <col width="18.42578125" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="74.42578125" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="23.42578125" customWidth="1" min="6" max="6"/>
+    <col width="42.85546875" customWidth="1" min="7" max="7"/>
+    <col width="37.85546875" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ফাইলের নাম</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ধরন</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Caption / Text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Schedule Time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>পোস্ট ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>নোট</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.png</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#bestrong #motivation #upliftinglife #lifelessons</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>46243.62708333333</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E2" s="4">
-        <v>46243.627083333333</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="5"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E54" s="6"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1,49 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Good Side\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28A8231-8693-4B9D-8F62-2AA99285D34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
   <sheets>
-    <sheet name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ফাইলের নাম</t>
+  </si>
+  <si>
+    <t>ধরন</t>
+  </si>
+  <si>
+    <t>Caption / Text</t>
+  </si>
+  <si>
+    <t>Schedule Time</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>পোস্ট ID</t>
+  </si>
+  <si>
+    <t>নোট</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>1.png</t>
+  </si>
+  <si>
+    <t>#bestrong #motivation #upliftinglife #lifelessons</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF856404"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF856404"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -92,96 +157,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -501,441 +507,413 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CAA70D-E652-488D-91B8-DAA4C7450532}">
   <dimension ref="A1:H54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="9.140625" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18.42578125" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="74.42578125" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="23.42578125" customWidth="1" min="6" max="6"/>
-    <col width="42.85546875" customWidth="1" min="7" max="7"/>
-    <col width="37.85546875" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="74.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="42.85546875" customWidth="1"/>
+    <col min="8" max="8" width="37.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ফাইলের নাম</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ধরন</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Caption / Text</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Schedule Time</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>পোস্ট ID</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>নোট</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.png</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>#bestrong #motivation #upliftinglife #lifelessons</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>46243.62708333333</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46243.645833333336</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="E16" s="4"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="E21" s="4"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="E24" s="4"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="E25" s="4"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="E26" s="4"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="5" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="E33" s="4"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="5" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="5" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="E35" s="4"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="E36" s="4"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="5" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="E37" s="4"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="5" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="E39" s="4"/>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="5" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="E40" s="4"/>
+      <c r="F40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="5" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="5" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="E42" s="4"/>
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="E43" s="4"/>
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="E44" s="4"/>
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="E45" s="4"/>
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="E46" s="4"/>
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="E47" s="4"/>
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="5" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="E48" s="4"/>
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="5" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="E49" s="4"/>
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="E51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="E52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="E53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="E54" s="6" t="n"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E54" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1,114 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Good Side\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28A8231-8693-4B9D-8F62-2AA99285D34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
+    <sheet name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>ফাইলের নাম</t>
-  </si>
-  <si>
-    <t>ধরন</t>
-  </si>
-  <si>
-    <t>Caption / Text</t>
-  </si>
-  <si>
-    <t>Schedule Time</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>পোস্ট ID</t>
-  </si>
-  <si>
-    <t>নোট</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>1.png</t>
-  </si>
-  <si>
-    <t>#bestrong #motivation #upliftinglife #lifelessons</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF856404"/>
       <sz val="10"/>
-      <color rgb="FF856404"/>
+    </font>
+    <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00155724"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -126,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,38 +102,100 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -507,413 +515,446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2CAA70D-E652-488D-91B8-DAA4C7450532}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="3"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="74.42578125" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="7" max="7" width="42.85546875" customWidth="1"/>
-    <col min="8" max="8" width="37.85546875" customWidth="1"/>
+    <col width="9.140625" customWidth="1" style="3" min="1" max="1"/>
+    <col width="18.42578125" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="74.42578125" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="23.42578125" customWidth="1" min="6" max="6"/>
+    <col width="42.85546875" customWidth="1" min="7" max="7"/>
+    <col width="37.85546875" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ফাইলের নাম</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ধরন</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Caption / Text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Schedule Time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>পোস্ট ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>নোট</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.png</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>#bestrong #motivation #upliftinglife #lifelessons</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>46243.64583333334</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1101748389190799</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E2" s="4">
-        <v>46243.645833333336</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="5"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="5"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="5"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="5"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="5"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="5"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="5"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E51" s="4"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E52" s="4"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E54" s="6"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -760,9 +760,14 @@
       <c r="E7" s="4" t="n">
         <v>46249.98125</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>27649665588048523</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -840,9 +840,14 @@
       <c r="E9" s="4" t="n">
         <v>46255.98125</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1683106826135038</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -873,9 +873,14 @@
       <c r="E10" s="4" t="n">
         <v>46256.04375</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1074633185107740</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -906,9 +906,14 @@
       <c r="E11" s="4" t="n">
         <v>46256.73125</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>894018050132253</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -939,9 +939,14 @@
       <c r="E12" s="4" t="n">
         <v>46256.98125</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1823612182135259</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -972,9 +972,14 @@
       <c r="E13" s="4" t="n">
         <v>46257.04375</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2769009403495258</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1005,9 +1005,14 @@
       <c r="E14" s="4" t="n">
         <v>46257.73125</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1530874442413260</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1038,9 +1038,14 @@
       <c r="E15" s="4" t="n">
         <v>46257.98125</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2280467659416494</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1071,9 +1071,14 @@
       <c r="E16" s="4" t="n">
         <v>46258.04375</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1452051307102444</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1104,9 +1104,14 @@
       <c r="E17" s="4" t="n">
         <v>46258.73125</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1587968476161034</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1137,9 +1137,14 @@
       <c r="E18" s="4" t="n">
         <v>46258.98125</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4207654702712754</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1170,9 +1170,14 @@
       <c r="E19" s="4" t="n">
         <v>46259.04375</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>992767813817459</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1203,9 +1203,14 @@
       <c r="E20" s="4" t="n">
         <v>46259.73125</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>27587787667584380</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1236,9 +1236,14 @@
       <c r="E21" s="4" t="n">
         <v>46259.98125</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1454347119839286</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1269,9 +1269,14 @@
       <c r="E22" s="4" t="n">
         <v>46260.04375</v>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1980528269148909</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1302,9 +1302,14 @@
       <c r="E23" s="4" t="n">
         <v>46260.73125</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1758022991882625</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1335,9 +1335,14 @@
       <c r="E24" s="4" t="n">
         <v>46260.98125</v>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1065045996510747</t>
         </is>
       </c>
     </row>
@@ -1363,9 +1368,14 @@
       <c r="E25" s="4" t="n">
         <v>46261.04375</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1689695918811692</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1401,9 +1401,14 @@
       <c r="E26" s="4" t="n">
         <v>46261.73125</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1780397206480342</t>
         </is>
       </c>
     </row>
@@ -1429,9 +1434,14 @@
       <c r="E27" s="4" t="n">
         <v>46261.98125</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1072410881952569</t>
         </is>
       </c>
     </row>
@@ -1457,9 +1467,14 @@
       <c r="E28" s="4" t="n">
         <v>46262.04375</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>945239394712203</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1500,9 +1500,14 @@
       <c r="E29" s="4" t="n">
         <v>46262.73125</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>911774668223700</t>
         </is>
       </c>
     </row>
@@ -1528,9 +1533,14 @@
       <c r="E30" s="4" t="n">
         <v>46262.98125</v>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1936512173696617</t>
         </is>
       </c>
     </row>
@@ -1556,9 +1566,14 @@
       <c r="E31" s="4" t="n">
         <v>46263.04375</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2022488668385006</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1599,9 +1599,14 @@
       <c r="E32" s="4" t="n">
         <v>46263.73125</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2896878417355974</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1632,9 +1632,14 @@
       <c r="E33" s="4" t="n">
         <v>46263.98125</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4565504850353412</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1665,9 +1665,14 @@
       <c r="E34" s="4" t="n">
         <v>46264.04375</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>4413516882195124</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1698,9 +1698,14 @@
       <c r="E35" s="4" t="n">
         <v>46264.73125</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1097868392813527</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1731,9 +1731,14 @@
       <c r="E36" s="4" t="n">
         <v>46264.98125</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1059533809783919</t>
         </is>
       </c>
     </row>
@@ -1759,9 +1764,14 @@
       <c r="E37" s="4" t="n">
         <v>46265.04375</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2730942240634248</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1797,9 +1797,14 @@
       <c r="E38" s="4" t="n">
         <v>46265.73125</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2476833956154394</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1830,9 +1830,14 @@
       <c r="E39" s="4" t="n">
         <v>46265.98125</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>909587595168218</t>
         </is>
       </c>
     </row>
@@ -1858,9 +1863,14 @@
       <c r="E40" s="4" t="n">
         <v>46266.04375</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2018462188800831</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1896,9 +1896,14 @@
       <c r="E41" s="4" t="n">
         <v>46266.73125</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1598417671924449</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1929,9 +1929,14 @@
       <c r="E42" s="4" t="n">
         <v>46266.98125</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1057404003792501</t>
         </is>
       </c>
     </row>
@@ -1957,9 +1962,14 @@
       <c r="E43" s="4" t="n">
         <v>46267.04375</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1074917661951402</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1995,9 +1995,14 @@
       <c r="E44" s="4" t="n">
         <v>46267.73125</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4656757961234588</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2028,9 +2028,14 @@
       <c r="E45" s="4" t="n">
         <v>46267.98125</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2288375808589293</t>
         </is>
       </c>
     </row>
@@ -2056,9 +2061,14 @@
       <c r="E46" s="4" t="n">
         <v>46268.04375</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2998714330486968</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2094,9 +2094,14 @@
       <c r="E47" s="4" t="n">
         <v>46268.73125</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1601613201378231</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2127,9 +2127,14 @@
       <c r="E48" s="4" t="n">
         <v>46268.98125</v>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1068613465536609</t>
         </is>
       </c>
     </row>
@@ -2155,9 +2160,14 @@
       <c r="E49" s="4" t="n">
         <v>46269.04375</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1616226950297775</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2193,9 +2193,14 @@
       <c r="E50" s="4" t="n">
         <v>46269.73125</v>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2230565810842922</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2226,9 +2226,14 @@
       <c r="E51" s="4" t="n">
         <v>46269.98125</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>976173482158021</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2259,9 +2259,14 @@
       <c r="E52" s="4" t="n">
         <v>46270.04375</v>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>28185353607758405</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2292,9 +2292,14 @@
       <c r="E53" s="4" t="n">
         <v>46270.73125</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1703778537395150</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2325,9 +2325,14 @@
       <c r="E54" s="4" t="n">
         <v>46270.98125</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1657309515909338</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2358,9 +2358,14 @@
       <c r="E55" s="4" t="n">
         <v>46271.04375</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1042572948603965</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2391,9 +2391,14 @@
       <c r="E56" s="4" t="n">
         <v>46271.73125</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>4375138459414555</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2424,9 +2424,14 @@
       <c r="E57" s="4" t="n">
         <v>46271.98125</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1609454037489507</t>
         </is>
       </c>
     </row>
@@ -2452,9 +2457,14 @@
       <c r="E58" s="4" t="n">
         <v>46272.04375</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2090163088557824</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2490,9 +2490,14 @@
       <c r="E59" s="4" t="n">
         <v>46272.73125</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1765757291337647</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2523,9 +2523,14 @@
       <c r="E60" s="4" t="n">
         <v>46272.98125</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1618842289876831</t>
         </is>
       </c>
     </row>
@@ -2551,9 +2556,14 @@
       <c r="E61" s="4" t="n">
         <v>46273.04375</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080461131545508</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2589,9 +2589,14 @@
       <c r="E62" s="4" t="n">
         <v>46273.73125</v>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1872285440459145</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2622,9 +2622,14 @@
       <c r="E63" s="4" t="n">
         <v>46273.98125</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1847037653141172</t>
         </is>
       </c>
     </row>
@@ -2650,9 +2655,14 @@
       <c r="E64" s="4" t="n">
         <v>46274.04375</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>4477315685930103</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2688,9 +2688,14 @@
       <c r="E65" s="4" t="n">
         <v>46274.73125</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1054914623831419</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2721,9 +2721,14 @@
       <c r="E66" s="4" t="n">
         <v>46274.98125</v>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1108002848883689</t>
         </is>
       </c>
     </row>
@@ -2749,9 +2754,14 @@
       <c r="E67" s="4" t="n">
         <v>46275.04375</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1105578792001030</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2787,9 +2787,14 @@
       <c r="E68" s="4" t="n">
         <v>46275.73125</v>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1076324914881590</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2820,9 +2820,14 @@
       <c r="E69" s="4" t="n">
         <v>46275.98125</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1816266079551128</t>
         </is>
       </c>
     </row>
@@ -2848,9 +2853,14 @@
       <c r="E70" s="4" t="n">
         <v>46276.04375</v>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1070531632374847</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2886,9 +2886,14 @@
       <c r="E71" s="4" t="n">
         <v>46276.73125</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>4126968904267807</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2919,9 +2919,14 @@
       <c r="E72" s="4" t="n">
         <v>46276.98125</v>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1710479280057111</t>
         </is>
       </c>
     </row>
@@ -2947,9 +2952,14 @@
       <c r="E73" s="4" t="n">
         <v>46277.04375</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1716874603780455</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2985,9 +2985,14 @@
       <c r="E74" s="4" t="n">
         <v>46277.73125</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2055172108537766</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3018,9 +3018,14 @@
       <c r="E75" s="4" t="n">
         <v>46277.98125</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1545043990993294</t>
         </is>
       </c>
     </row>
